--- a/mesures/TP_mesures_By_William.xlsx
+++ b/mesures/TP_mesures_By_William.xlsx
@@ -5,10 +5,11 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="LOC" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="CC" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -20,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="55">
   <si>
     <t xml:space="preserve">Mesure LOC (Lines Of Code) - projet BAGNIS-MARCUS-PIBOULEAU</t>
   </si>
@@ -65,6 +66,126 @@
   </si>
   <si>
     <t xml:space="preserve">Le périmètre ./app exclut .html, .sql, .json, .md, .yml.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Complexité cyclomatique (CC) - iqsort0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nœuds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arêtes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calcul de V(G) = E - N + 2P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nœud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Instruction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lignes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">De</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E (arêtes)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">if (n &lt;= 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3-4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N (nœuds)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">return</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P (composantes connexes)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">i = 1, j = 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V(G) = E - N + 2P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">i &lt; n ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contrôle : décisions + 1 (3 décisions : lignes 4, 6, 7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a[i] &lt; a[0] ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">swap(++j, i, a)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contrôle : écart avec V(G)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">i++</t>
+  </si>
+  <si>
+    <t xml:space="preserve">swap + 2 appels iqsort0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sortie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12</t>
   </si>
 </sst>
 </file>
@@ -472,7 +593,8 @@
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="24.06"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="24"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -574,4 +696,387 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:I20"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="1"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="1"/>
+      <c r="E4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" s="1"/>
+      <c r="H4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <f aca="false">COUNTA(E5:E15)</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="1"/>
+      <c r="E5" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" s="1"/>
+      <c r="H5" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <f aca="false">COUNTA(A5:A13)</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="1"/>
+      <c r="E6" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" s="1"/>
+      <c r="H6" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" s="1"/>
+      <c r="E7" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7" s="1"/>
+      <c r="H7" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="I7" s="9" t="n">
+        <f aca="false">I4-I5+2*I6</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" s="1"/>
+      <c r="E8" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G8" s="1"/>
+      <c r="H8" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" s="1"/>
+      <c r="E9" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+    </row>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" s="1"/>
+      <c r="E10" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="G10" s="1"/>
+      <c r="H10" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <f aca="false">I7-I8</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" s="1"/>
+      <c r="E11" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+    </row>
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D12" s="1"/>
+      <c r="E12" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="G12" s="1"/>
+      <c r="H12" s="9"/>
+      <c r="I12" s="1"/>
+    </row>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D13" s="1"/>
+      <c r="E13" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="G13" s="1"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="1"/>
+    </row>
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G14" s="1"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="1"/>
+    </row>
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="G15" s="1"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="1"/>
+    </row>
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="1"/>
+    </row>
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+    </row>
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+    </row>
+    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+    </row>
+    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>
--- a/mesures/TP_mesures_By_William.xlsx
+++ b/mesures/TP_mesures_By_William.xlsx
@@ -5,11 +5,12 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="LOC" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="CC" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="halstead" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -21,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="95">
   <si>
     <t xml:space="preserve">Mesure LOC (Lines Of Code) - projet BAGNIS-MARCUS-PIBOULEAU</t>
   </si>
@@ -186,18 +187,140 @@
   </si>
   <si>
     <t xml:space="preserve">12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Métriques de Halstead - iqsort0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Opérateurs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Opérandes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mesures</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Opérateur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Occurrences</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Opérande</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nt (opérateurs distincts)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">void</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iqsort0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nt (occurrences d'opérateurs)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">( )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">swap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nd (opérandes distincts)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">int</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nd (occurrences d'opérandes)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Longueur N = Nt + Nd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">i</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vocabulaire n = nt + nd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{ }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">j</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Volume = N * log2(n)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Difficulté = (nt/2) * (Nd/nd)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">if</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Effort = Difficulté * Volume</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;=</t>
+  </si>
+  <si>
+    <t xml:space="preserve">for</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">++</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ ]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="167" formatCode="0.00"/>
+    <numFmt numFmtId="168" formatCode="#,##0.00"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -247,6 +370,32 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -296,7 +445,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="17">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -334,6 +483,34 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1079,4 +1256,395 @@
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:H22"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="H3" s="1"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="C4" s="1"/>
+      <c r="D4" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="F4" s="1"/>
+      <c r="G4" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="H4" s="13" t="n">
+        <f aca="false">COUNTA(A5:A21)</f>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="B5" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="1"/>
+      <c r="D5" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="E5" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" s="1"/>
+      <c r="G5" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="H5" s="13" t="n">
+        <f aca="false">SUM(B5:B21)</f>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="B6" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="C6" s="1"/>
+      <c r="D6" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="E6" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" s="1"/>
+      <c r="G6" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="H6" s="13" t="n">
+        <f aca="false">COUNTA(D5:D12)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="B7" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" s="1"/>
+      <c r="D7" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="E7" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="F7" s="1"/>
+      <c r="G7" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="H7" s="13" t="n">
+        <f aca="false">SUM(E5:E12)</f>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="B8" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="1"/>
+      <c r="D8" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="E8" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="F8" s="1"/>
+      <c r="G8" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="H8" s="13" t="n">
+        <f aca="false">H5+H7</f>
+        <v>84</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="B9" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="C9" s="1"/>
+      <c r="D9" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="E9" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="F9" s="1"/>
+      <c r="G9" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="H9" s="13" t="n">
+        <f aca="false">H4+H6</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="B10" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="1"/>
+      <c r="D10" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="E10" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="F10" s="1"/>
+      <c r="G10" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="H10" s="15" t="n">
+        <f aca="false">H8*LOG(H9,2)</f>
+        <v>390.083919941077</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="B11" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="C11" s="1"/>
+      <c r="D11" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="E11" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" s="1"/>
+      <c r="G11" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="H11" s="15" t="n">
+        <f aca="false">(H4/2)*(H7/H6)</f>
+        <v>38.25</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="B12" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" s="1"/>
+      <c r="D12" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="E12" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="F12" s="1"/>
+      <c r="G12" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="H12" s="16" t="n">
+        <f aca="false">H11*H10</f>
+        <v>14920.7099377462</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="B13" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+    </row>
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="1"/>
+    </row>
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="B15" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="13"/>
+      <c r="H15" s="1"/>
+    </row>
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="B16" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="13"/>
+      <c r="H16" s="1"/>
+    </row>
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="B17" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="13"/>
+      <c r="H17" s="1"/>
+    </row>
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="B18" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="1"/>
+    </row>
+    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="B19" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="1"/>
+    </row>
+    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="B20" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="13"/>
+      <c r="H20" s="1"/>
+    </row>
+    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="B21" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+    </row>
+    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>
--- a/mesures/TP_mesures_By_William.xlsx
+++ b/mesures/TP_mesures_By_William.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="98">
   <si>
     <t xml:space="preserve">Mesure LOC (Lines Of Code) - projet BAGNIS-MARCUS-PIBOULEAU</t>
   </si>
@@ -307,6 +307,15 @@
   </si>
   <si>
     <t xml:space="preserve">-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Question 7 - Validité des mesures de Halstead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Selon la théorie de la mesure, la validité d'une métrique repose sur sa capacité à évaluer avec exactitude l'attribut ciblé. Elle doit traduire fidèlement la réalité empirique, par exemple en attribuant une valeur supérieure à un code reconnu comme plus complexe. De plus, sa définition se doit d'être parfaitement claire pour garantir la reproductibilité des résultats d'un évaluateur à l'autre. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toutefois, les mesures de Halstead présentent des compteurs de base ambigus. Étant donné que deux personnes analysant exactement le même code peuvent aboutir à des résultats divergents, il est impossible de certifier que ces métriques quantifient correctement ce qu'elles sont censées représenter.</t>
   </si>
 </sst>
 </file>
@@ -320,7 +329,7 @@
     <numFmt numFmtId="167" formatCode="0.00"/>
     <numFmt numFmtId="168" formatCode="#,##0.00"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -376,6 +385,29 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="0"/>
     </font>
     <font>
       <b val="true"/>
@@ -385,16 +417,10 @@
       <family val="0"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="0"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -445,7 +471,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -502,16 +528,24 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="167" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="168" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1263,7 +1297,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:P25"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1328,17 +1362,17 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="14" t="s">
+      <c r="A5" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="B5" s="14" t="n">
+      <c r="B5" s="13" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="1"/>
-      <c r="D5" s="14" t="s">
+      <c r="D5" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="E5" s="14" t="n">
+      <c r="E5" s="13" t="n">
         <v>3</v>
       </c>
       <c r="F5" s="1"/>
@@ -1351,17 +1385,17 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="B6" s="14" t="n">
+      <c r="B6" s="13" t="n">
         <v>8</v>
       </c>
       <c r="C6" s="1"/>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="E6" s="14" t="n">
+      <c r="E6" s="13" t="n">
         <v>2</v>
       </c>
       <c r="F6" s="1"/>
@@ -1374,17 +1408,17 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="14" t="s">
+      <c r="A7" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="B7" s="14" t="n">
+      <c r="B7" s="13" t="n">
         <v>3</v>
       </c>
       <c r="C7" s="1"/>
-      <c r="D7" s="14" t="s">
+      <c r="D7" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="E7" s="14" t="n">
+      <c r="E7" s="13" t="n">
         <v>7</v>
       </c>
       <c r="F7" s="1"/>
@@ -1397,17 +1431,17 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="14" t="s">
+      <c r="A8" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="B8" s="14" t="n">
+      <c r="B8" s="13" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="1"/>
-      <c r="D8" s="14" t="s">
+      <c r="D8" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="E8" s="14" t="n">
+      <c r="E8" s="13" t="n">
         <v>4</v>
       </c>
       <c r="F8" s="1"/>
@@ -1420,17 +1454,17 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="14" t="s">
+      <c r="A9" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="B9" s="14" t="n">
+      <c r="B9" s="13" t="n">
         <v>9</v>
       </c>
       <c r="C9" s="1"/>
-      <c r="D9" s="14" t="s">
+      <c r="D9" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="E9" s="14" t="n">
+      <c r="E9" s="13" t="n">
         <v>6</v>
       </c>
       <c r="F9" s="1"/>
@@ -1443,79 +1477,79 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="14" t="s">
+      <c r="A10" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="B10" s="14" t="n">
+      <c r="B10" s="13" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="1"/>
-      <c r="D10" s="14" t="s">
+      <c r="D10" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="E10" s="14" t="n">
+      <c r="E10" s="13" t="n">
         <v>7</v>
       </c>
       <c r="F10" s="1"/>
       <c r="G10" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="H10" s="15" t="n">
+      <c r="H10" s="14" t="n">
         <f aca="false">H8*LOG(H9,2)</f>
         <v>390.083919941077</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="14" t="s">
+      <c r="A11" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="B11" s="14" t="n">
+      <c r="B11" s="13" t="n">
         <v>8</v>
       </c>
       <c r="C11" s="1"/>
-      <c r="D11" s="14" t="s">
+      <c r="D11" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="E11" s="14" t="n">
+      <c r="E11" s="13" t="n">
         <v>3</v>
       </c>
       <c r="F11" s="1"/>
       <c r="G11" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="H11" s="15" t="n">
+      <c r="H11" s="14" t="n">
         <f aca="false">(H4/2)*(H7/H6)</f>
         <v>38.25</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="14" t="s">
+      <c r="A12" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="B12" s="14" t="n">
+      <c r="B12" s="13" t="n">
         <v>2</v>
       </c>
       <c r="C12" s="1"/>
-      <c r="D12" s="14" t="s">
+      <c r="D12" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="E12" s="14" t="n">
+      <c r="E12" s="13" t="n">
         <v>4</v>
       </c>
       <c r="F12" s="1"/>
       <c r="G12" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="H12" s="16" t="n">
+      <c r="H12" s="15" t="n">
         <f aca="false">H11*H10</f>
         <v>14920.7099377462</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="14" t="s">
+      <c r="A13" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="B13" s="14" t="n">
+      <c r="B13" s="13" t="n">
         <v>1</v>
       </c>
       <c r="C13" s="1"/>
@@ -1526,10 +1560,10 @@
       <c r="H13" s="1"/>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="14" t="s">
+      <c r="A14" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="14" t="n">
+      <c r="B14" s="13" t="n">
         <v>1</v>
       </c>
       <c r="C14" s="1"/>
@@ -1540,10 +1574,10 @@
       <c r="H14" s="1"/>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="14" t="s">
+      <c r="A15" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="B15" s="14" t="n">
+      <c r="B15" s="13" t="n">
         <v>1</v>
       </c>
       <c r="C15" s="1"/>
@@ -1554,10 +1588,10 @@
       <c r="H15" s="1"/>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="14" t="s">
+      <c r="A16" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="B16" s="14" t="n">
+      <c r="B16" s="13" t="n">
         <v>2</v>
       </c>
       <c r="C16" s="1"/>
@@ -1568,10 +1602,10 @@
       <c r="H16" s="1"/>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="14" t="s">
+      <c r="A17" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="B17" s="14" t="n">
+      <c r="B17" s="13" t="n">
         <v>2</v>
       </c>
       <c r="C17" s="1"/>
@@ -1582,10 +1616,10 @@
       <c r="H17" s="1"/>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="14" t="s">
+      <c r="A18" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="B18" s="14" t="n">
+      <c r="B18" s="13" t="n">
         <v>2</v>
       </c>
       <c r="C18" s="1"/>
@@ -1596,10 +1630,10 @@
       <c r="H18" s="1"/>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="14" t="s">
+      <c r="A19" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="B19" s="14" t="n">
+      <c r="B19" s="13" t="n">
         <v>2</v>
       </c>
       <c r="C19" s="1"/>
@@ -1610,10 +1644,10 @@
       <c r="H19" s="1"/>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="14" t="s">
+      <c r="A20" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="B20" s="14" t="n">
+      <c r="B20" s="13" t="n">
         <v>2</v>
       </c>
       <c r="C20" s="1"/>
@@ -1624,10 +1658,10 @@
       <c r="H20" s="1"/>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="14" t="s">
+      <c r="A21" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="B21" s="14" t="n">
+      <c r="B21" s="13" t="n">
         <v>2</v>
       </c>
       <c r="C21" s="1"/>
@@ -1637,8 +1671,59 @@
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
     </row>
-    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I22" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="J22" s="16"/>
+      <c r="K22" s="16"/>
+      <c r="L22" s="16"/>
+      <c r="M22" s="16"/>
+      <c r="N22" s="16"/>
+      <c r="O22" s="16"/>
+      <c r="P22" s="16"/>
+    </row>
+    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I23" s="17"/>
+      <c r="J23" s="17"/>
+      <c r="K23" s="17"/>
+      <c r="L23" s="17"/>
+      <c r="M23" s="17"/>
+      <c r="N23" s="17"/>
+      <c r="O23" s="17"/>
+      <c r="P23" s="17"/>
+    </row>
+    <row r="24" customFormat="false" ht="46.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I24" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="J24" s="18"/>
+      <c r="K24" s="18"/>
+      <c r="L24" s="18"/>
+      <c r="M24" s="18"/>
+      <c r="N24" s="18"/>
+      <c r="O24" s="18"/>
+      <c r="P24" s="18"/>
+    </row>
+    <row r="25" customFormat="false" ht="35.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I25" s="18" t="s">
+        <v>97</v>
+      </c>
+      <c r="J25" s="18"/>
+      <c r="K25" s="18"/>
+      <c r="L25" s="18"/>
+      <c r="M25" s="18"/>
+      <c r="N25" s="18"/>
+      <c r="O25" s="18"/>
+      <c r="P25" s="18"/>
+    </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="I22:P22"/>
+    <mergeCell ref="I23:P23"/>
+    <mergeCell ref="I24:P24"/>
+    <mergeCell ref="I25:P25"/>
+  </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/mesures/TP_mesures_By_William.xlsx
+++ b/mesures/TP_mesures_By_William.xlsx
@@ -5,12 +5,13 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="LOC" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="CC" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="halstead" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="albrecht" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -22,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="114">
   <si>
     <t xml:space="preserve">Mesure LOC (Lines Of Code) - projet BAGNIS-MARCUS-PIBOULEAU</t>
   </si>
@@ -316,6 +317,56 @@
   </si>
   <si>
     <t xml:space="preserve">Toutefois, les mesures de Halstead présentent des compteurs de base ambigus. Étant donné que deux personnes analysant exactement le même code peuvent aboutir à des résultats divergents, il est impossible de certifier que ces métriques quantifient correctement ce qu'elles sont censées représenter.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Score UFC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Catégorie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calcul</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sous-total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entrées externes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3×4 + 4×3 + 6×1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sorties externes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4×0 + 5×2 + 7×1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Requêtes externes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3×7 + 4×0 + 6×0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fichiers internes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7×3 + 10×0 + 15×0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fichiers externes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5×0 + 7×5 + 10×2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pour établir des poids, on part de l'intuition que tous les éléments d'un système ne demandent pas le même travail. Dans un site marchand, un écran d'alerte « saisie incorrecte » se fait en quelques minutes, alors qu'un formulaire de saisie demande des champs, des contrôles et un enregistrement. On les range donc par niveaux (simple, moyen, difficile) en comparant leur complexité.
+Pour chiffrer ces niveaux, on prend un élément simple comme référence, par exemple 3, et on en déduit les autres. Un moyen vaut un peu plus, un difficile à peu près le double. On peut aussi s'appuyer sur le temps réellement passé sur des projets précédents, ou demander l'avis de plusieurs développeurs expérimentés.
+Les poids restent donc en partie subjectifs : ils dépendent de l'équipe et des technologies, et il faut les réajuster au fil des projets.</t>
   </si>
 </sst>
 </file>
@@ -329,7 +380,7 @@
     <numFmt numFmtId="167" formatCode="0.00"/>
     <numFmt numFmtId="168" formatCode="#,##0.00"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -408,6 +459,27 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="0"/>
     </font>
     <font>
       <b val="true"/>
@@ -417,13 +489,13 @@
       <family val="0"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
+      <name val="Arial"/>
+      <family val="0"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -434,6 +506,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFD9E1F2"/>
         <bgColor rgb="FFCCFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2A6099"/>
+        <bgColor rgb="FF666699"/>
       </patternFill>
     </fill>
   </fills>
@@ -471,7 +549,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="27">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -536,15 +614,47 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -581,7 +691,7 @@
       <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FF2A6099"/>
       <rgbColor rgb="FFD9E1F2"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
@@ -1732,4 +1842,124 @@
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+    </row>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>100</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="B4" s="22" t="s">
+        <v>103</v>
+      </c>
+      <c r="C4" s="22" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="B5" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="C5" s="22" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="B6" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="C6" s="22" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="B7" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="C7" s="22" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="22" t="s">
+        <v>110</v>
+      </c>
+      <c r="B8" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="C8" s="22" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="B9" s="22"/>
+      <c r="C9" s="24" t="n">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="25"/>
+      <c r="B10" s="25"/>
+      <c r="C10" s="25"/>
+    </row>
+    <row r="11" customFormat="false" ht="191.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="26" t="s">
+        <v>113</v>
+      </c>
+      <c r="B11" s="26"/>
+      <c r="C11" s="26"/>
+      <c r="D11" s="26"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="26"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A11:F11"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>
--- a/mesures/TP_mesures_By_William.xlsx
+++ b/mesures/TP_mesures_By_William.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="128">
   <si>
     <t xml:space="preserve">Mesure LOC (Lines Of Code) - projet BAGNIS-MARCUS-PIBOULEAU</t>
   </si>
@@ -367,6 +367,49 @@
     <t xml:space="preserve">Pour établir des poids, on part de l'intuition que tous les éléments d'un système ne demandent pas le même travail. Dans un site marchand, un écran d'alerte « saisie incorrecte » se fait en quelques minutes, alors qu'un formulaire de saisie demande des champs, des contrôles et un enregistrement. On les range donc par niveaux (simple, moyen, difficile) en comparant leur complexité.
 Pour chiffrer ces niveaux, on prend un élément simple comme référence, par exemple 3, et on en déduit les autres. Un moyen vaut un peu plus, un difficile à peu près le double. On peut aussi s'appuyer sur le temps réellement passé sur des projets précédents, ou demander l'avis de plusieurs développeurs expérimentés.
 Les poids restent donc en partie subjectifs : ils dépendent de l'équipe et des technologies, et il faut les réajuster au fil des projets.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Poids (simple / moyen / difficile)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scores (simple / moyen / difficile)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 / 2 / 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 / 1 / 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1×1 + 2×1 + 4×0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 / 3 / 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 / 1 / 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2×0 + 3×1 + 5×0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 / 0 / 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1×0 + 2×0 + 4×0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 / 5 / 8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3×0 + 5×0 + 0×0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+3 / 5 / 8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3×0 + 5×0 + 8×0</t>
   </si>
 </sst>
 </file>
@@ -380,7 +423,7 @@
     <numFmt numFmtId="167" formatCode="0.00"/>
     <numFmt numFmtId="168" formatCode="#,##0.00"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -469,33 +512,14 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
-      <sz val="13"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="0"/>
+      <charset val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -512,6 +536,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF2A6099"/>
         <bgColor rgb="FF666699"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFCC"/>
       </patternFill>
     </fill>
   </fills>
@@ -549,7 +579,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="31">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -626,36 +656,52 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1849,106 +1895,239 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="20" t="s">
         <v>99</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="C3" s="21" t="s">
+      <c r="C3" s="20" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="C4" s="22" t="n">
+      <c r="C4" s="21" t="n">
         <v>30</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="C5" s="22" t="n">
+      <c r="C5" s="21" t="n">
         <v>17</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="22" t="s">
+      <c r="A6" s="21" t="s">
         <v>106</v>
       </c>
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="21" t="s">
         <v>107</v>
       </c>
-      <c r="C6" s="22" t="n">
+      <c r="C6" s="21" t="n">
         <v>21</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="22" t="s">
+      <c r="A7" s="21" t="s">
         <v>108</v>
       </c>
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="21" t="s">
         <v>109</v>
       </c>
-      <c r="C7" s="22" t="n">
+      <c r="C7" s="21" t="n">
         <v>21</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="22" t="s">
+      <c r="A8" s="21" t="s">
         <v>110</v>
       </c>
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="21" t="s">
         <v>111</v>
       </c>
-      <c r="C8" s="22" t="n">
+      <c r="C8" s="21" t="n">
         <v>55</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="23" t="s">
+      <c r="A9" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="B9" s="22"/>
-      <c r="C9" s="24" t="n">
+      <c r="B9" s="21"/>
+      <c r="C9" s="22" t="n">
         <v>144</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="25"/>
-      <c r="B10" s="25"/>
-      <c r="C10" s="25"/>
+      <c r="A10" s="23"/>
+      <c r="B10" s="23"/>
+      <c r="C10" s="23"/>
     </row>
     <row r="11" customFormat="false" ht="191.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="26" t="s">
+      <c r="A11" s="24" t="s">
         <v>113</v>
       </c>
-      <c r="B11" s="26"/>
-      <c r="C11" s="26"/>
-      <c r="D11" s="26"/>
-      <c r="E11" s="26"/>
-      <c r="F11" s="26"/>
+      <c r="B11" s="24"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="24"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="24"/>
+    </row>
+    <row r="16" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="25" t="s">
+        <v>99</v>
+      </c>
+      <c r="B16" s="25" t="s">
+        <v>114</v>
+      </c>
+      <c r="C16" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="D16" s="26"/>
+      <c r="E16" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="F16" s="27" t="s">
+        <v>100</v>
+      </c>
+      <c r="G16" s="27" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="28" t="s">
+        <v>102</v>
+      </c>
+      <c r="B17" s="28" t="s">
+        <v>116</v>
+      </c>
+      <c r="C17" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="E17" s="28" t="s">
+        <v>102</v>
+      </c>
+      <c r="F17" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="G17" s="28" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="28" t="s">
+        <v>104</v>
+      </c>
+      <c r="B18" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="C18" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="E18" s="28" t="s">
+        <v>104</v>
+      </c>
+      <c r="F18" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="G18" s="28" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="28" t="s">
+        <v>106</v>
+      </c>
+      <c r="B19" s="28" t="s">
+        <v>116</v>
+      </c>
+      <c r="C19" s="28" t="s">
+        <v>122</v>
+      </c>
+      <c r="E19" s="28" t="s">
+        <v>106</v>
+      </c>
+      <c r="F19" s="28" t="s">
+        <v>123</v>
+      </c>
+      <c r="G19" s="28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="28" t="s">
+        <v>108</v>
+      </c>
+      <c r="B20" s="28" t="s">
+        <v>124</v>
+      </c>
+      <c r="C20" s="28" t="s">
+        <v>122</v>
+      </c>
+      <c r="E20" s="28" t="s">
+        <v>108</v>
+      </c>
+      <c r="F20" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="G20" s="28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="28" t="s">
+        <v>110</v>
+      </c>
+      <c r="B21" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="C21" s="28" t="s">
+        <v>122</v>
+      </c>
+      <c r="E21" s="28" t="s">
+        <v>110</v>
+      </c>
+      <c r="F21" s="28" t="s">
+        <v>127</v>
+      </c>
+      <c r="G21" s="28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="29"/>
+      <c r="B22" s="28"/>
+      <c r="C22" s="30"/>
+      <c r="E22" s="29" t="s">
+        <v>112</v>
+      </c>
+      <c r="F22" s="28"/>
+      <c r="G22" s="30" t="n">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/mesures/TP_mesures_By_William.xlsx
+++ b/mesures/TP_mesures_By_William.xlsx
@@ -5,13 +5,14 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="LOC" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="CC" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="halstead" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="albrecht" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="MI" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="135">
   <si>
     <t xml:space="preserve">Mesure LOC (Lines Of Code) - projet BAGNIS-MARCUS-PIBOULEAU</t>
   </si>
@@ -410,6 +411,27 @@
   </si>
   <si>
     <t xml:space="preserve">3×0 + 5×0 + 8×0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Index of maintenability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">171 - 5,2ln(HV) - 0,23CC - 16,2ln(LOC) + 50sin * sqrt(2,46COM)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Volume d’Halstead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Complexité cyclomatique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nombre de lignes de code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pourcentage de lignes de code qui sont des commentaires</t>
+  </si>
+  <si>
+    <t xml:space="preserve">171 - 5,2 * ln(390,08) - 0,23 * 4 - 16,2 * ln(12) + 0 = 171 − 31,03 − 0,92 − 40,26 ≈ 98,80</t>
   </si>
 </sst>
 </file>
@@ -519,7 +541,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -535,13 +557,19 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF2A6099"/>
-        <bgColor rgb="FF666699"/>
+        <bgColor rgb="FF3366FF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5983B0"/>
+        <bgColor rgb="FF808080"/>
       </patternFill>
     </fill>
   </fills>
@@ -680,28 +708,28 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -761,7 +789,7 @@
       <rgbColor rgb="FFFFCC00"/>
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF5983B0"/>
       <rgbColor rgb="FF969696"/>
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF339966"/>
@@ -1996,6 +2024,10 @@
       <c r="E11" s="24"/>
       <c r="F11" s="24"/>
     </row>
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="16" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="25" t="s">
         <v>99</v>
@@ -2007,125 +2039,125 @@
         <v>115</v>
       </c>
       <c r="D16" s="26"/>
-      <c r="E16" s="27" t="s">
+      <c r="E16" s="20" t="s">
         <v>99</v>
       </c>
-      <c r="F16" s="27" t="s">
+      <c r="F16" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="27" t="s">
+      <c r="G16" s="20" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="28" t="s">
+      <c r="A17" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="B17" s="28" t="s">
+      <c r="B17" s="21" t="s">
         <v>116</v>
       </c>
-      <c r="C17" s="28" t="s">
+      <c r="C17" s="21" t="s">
         <v>117</v>
       </c>
-      <c r="E17" s="28" t="s">
+      <c r="E17" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="F17" s="28" t="s">
+      <c r="F17" s="21" t="s">
         <v>118</v>
       </c>
-      <c r="G17" s="28" t="n">
+      <c r="G17" s="21" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="28" t="s">
+      <c r="A18" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="B18" s="28" t="s">
+      <c r="B18" s="21" t="s">
         <v>119</v>
       </c>
-      <c r="C18" s="28" t="s">
+      <c r="C18" s="21" t="s">
         <v>120</v>
       </c>
-      <c r="E18" s="28" t="s">
+      <c r="E18" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="F18" s="28" t="s">
+      <c r="F18" s="21" t="s">
         <v>121</v>
       </c>
-      <c r="G18" s="28" t="n">
+      <c r="G18" s="21" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="28" t="s">
+      <c r="A19" s="21" t="s">
         <v>106</v>
       </c>
-      <c r="B19" s="28" t="s">
+      <c r="B19" s="21" t="s">
         <v>116</v>
       </c>
-      <c r="C19" s="28" t="s">
+      <c r="C19" s="21" t="s">
         <v>122</v>
       </c>
-      <c r="E19" s="28" t="s">
+      <c r="E19" s="21" t="s">
         <v>106</v>
       </c>
-      <c r="F19" s="28" t="s">
+      <c r="F19" s="21" t="s">
         <v>123</v>
       </c>
-      <c r="G19" s="28" t="n">
+      <c r="G19" s="21" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="28" t="s">
+      <c r="A20" s="21" t="s">
         <v>108</v>
       </c>
-      <c r="B20" s="28" t="s">
+      <c r="B20" s="21" t="s">
         <v>124</v>
       </c>
-      <c r="C20" s="28" t="s">
+      <c r="C20" s="21" t="s">
         <v>122</v>
       </c>
-      <c r="E20" s="28" t="s">
+      <c r="E20" s="21" t="s">
         <v>108</v>
       </c>
-      <c r="F20" s="28" t="s">
+      <c r="F20" s="21" t="s">
         <v>125</v>
       </c>
-      <c r="G20" s="28" t="n">
+      <c r="G20" s="21" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="28" t="s">
+      <c r="A21" s="21" t="s">
         <v>110</v>
       </c>
-      <c r="B21" s="28" t="s">
+      <c r="B21" s="21" t="s">
         <v>126</v>
       </c>
-      <c r="C21" s="28" t="s">
+      <c r="C21" s="21" t="s">
         <v>122</v>
       </c>
-      <c r="E21" s="28" t="s">
+      <c r="E21" s="21" t="s">
         <v>110</v>
       </c>
-      <c r="F21" s="28" t="s">
+      <c r="F21" s="21" t="s">
         <v>127</v>
       </c>
-      <c r="G21" s="28" t="n">
+      <c r="G21" s="21" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="29"/>
-      <c r="B22" s="28"/>
-      <c r="C22" s="30"/>
-      <c r="E22" s="29" t="s">
+      <c r="A22" s="13"/>
+      <c r="B22" s="21"/>
+      <c r="C22" s="22"/>
+      <c r="E22" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="F22" s="28"/>
-      <c r="G22" s="30" t="n">
+      <c r="F22" s="21"/>
+      <c r="G22" s="22" t="n">
         <v>6</v>
       </c>
     </row>
@@ -2141,4 +2173,98 @@
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:H18"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+    </row>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="28" t="s">
+        <v>100</v>
+      </c>
+      <c r="B7" s="28"/>
+      <c r="C7" s="28"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="28"/>
+      <c r="H7" s="28"/>
+    </row>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="29" t="s">
+        <v>129</v>
+      </c>
+      <c r="B9" s="29"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="29"/>
+      <c r="F9" s="30" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F10" s="30" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F11" s="30" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F12" s="30" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="29" t="s">
+        <v>134</v>
+      </c>
+      <c r="B16" s="29"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="29"/>
+      <c r="E16" s="29"/>
+      <c r="F16" s="29"/>
+    </row>
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A16:F16"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>
--- a/mesures/TP_mesures_By_William.xlsx
+++ b/mesures/TP_mesures_By_William.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="140">
   <si>
     <t xml:space="preserve">Mesure LOC (Lines Of Code) - projet BAGNIS-MARCUS-PIBOULEAU</t>
   </si>
@@ -419,19 +419,58 @@
     <t xml:space="preserve">171 - 5,2ln(HV) - 0,23CC - 16,2ln(LOC) + 50sin * sqrt(2,46COM)</t>
   </si>
   <si>
-    <t xml:space="preserve">Volume d’Halstead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Complexité cyclomatique</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nombre de lignes de code</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pourcentage de lignes de code qui sont des commentaires</t>
+    <t xml:space="preserve">Volume d’Halstead (HV)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Complexité cyclomatique (CC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nombre de lignes de code (LOC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pourcentage de lignes de code qui sont des commentaires (COM)</t>
   </si>
   <si>
     <t xml:space="preserve">171 - 5,2 * ln(390,08) - 0,23 * 4 - 16,2 * ln(12) + 0 = 171 − 31,03 − 0,92 − 40,26 ≈ 98,80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calcul avec COM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0,52 ( 13 /24 )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">171 - 5,2 * ln(390,08) - 0,23 * 4 - 16,2 * ln(12) + 50 * sin * sqrt(2,46 * 0,52 ) = 171 − 31,03 − 0,92 − 40,26 + 45,24  ≈ 144,04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On voit que le score est plus elevé avec les commentaires vraiment c une singerie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/*
+ * Auteur      : Prénom NOM
+ * Date        : 08/10/2026
+ * Description : QuickSort simplifié (Bentley et McIlroy, 1993).
+ *               Trie en place les n premiers éléments du tableau a,
+ *               par ordre croissant.
+ */
+void iqsort0 ( int *a , int n )
+{
+    int i , j ;
+    // Cas de base : un tableau de 0 ou 1 élément est déjà trié
+    if ( n &lt;=1)
+        return ;
+    // Partitionnement autour du pivot a[0] : j = indice du dernier élément &lt; pivot
+    for ( i = 1 , j = 0; i &lt; n ; i ++)
+    // Si a[i] est plus petit que le pivot, on l'ajoute à la zone de gauche
+        if ( a [ i ] &lt; a [0])
+            swap (++ j , i , a );
+    // Place le pivot à sa position définitive j
+    swap (0 , j , a );
+    // Tri récursif de la partie gauche (éléments &lt; pivot)
+    iqsort0 (a , j );
+    // Tri récursif de la partie droite (éléments &gt;= pivot)
+    iqsort0 ( a + j +1 , n -j -1);
+}</t>
   </si>
 </sst>
 </file>
@@ -607,7 +646,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="33">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -716,7 +755,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -725,11 +776,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -2180,7 +2227,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:Q34"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2221,20 +2268,38 @@
       <c r="F9" s="30" t="s">
         <v>130</v>
       </c>
+      <c r="J9" s="30" t="n">
+        <v>390.08</v>
+      </c>
+      <c r="L9" s="29" t="s">
+        <v>129</v>
+      </c>
+      <c r="M9" s="29"/>
+      <c r="N9" s="29"/>
+      <c r="O9" s="29"/>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F10" s="30" t="s">
         <v>131</v>
       </c>
+      <c r="J10" s="30" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F11" s="30" t="s">
         <v>132</v>
       </c>
+      <c r="J11" s="30" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F12" s="30" t="s">
         <v>133</v>
+      </c>
+      <c r="J12" s="30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -2249,15 +2314,111 @@
       <c r="D16" s="29"/>
       <c r="E16" s="29"/>
       <c r="F16" s="29"/>
+      <c r="L16" s="29" t="s">
+        <v>134</v>
+      </c>
+      <c r="M16" s="29"/>
+      <c r="N16" s="29"/>
+      <c r="O16" s="29"/>
+      <c r="P16" s="29"/>
+      <c r="Q16" s="29"/>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="31" t="s">
+        <v>135</v>
+      </c>
+      <c r="B20" s="31"/>
+      <c r="C20" s="31"/>
+      <c r="D20" s="31"/>
+      <c r="E20" s="31"/>
+      <c r="F20" s="31"/>
+      <c r="G20" s="31"/>
+      <c r="H20" s="31"/>
+    </row>
+    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="29" t="s">
+        <v>129</v>
+      </c>
+      <c r="B23" s="29"/>
+      <c r="C23" s="29"/>
+      <c r="D23" s="29"/>
+      <c r="F23" s="30" t="s">
+        <v>130</v>
+      </c>
+      <c r="J23" s="30" t="n">
+        <v>390.08</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F24" s="30" t="s">
+        <v>131</v>
+      </c>
+      <c r="J24" s="30" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F25" s="30" t="s">
+        <v>132</v>
+      </c>
+      <c r="J25" s="30" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F26" s="30" t="s">
+        <v>133</v>
+      </c>
+      <c r="J26" s="30" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="29" t="s">
+        <v>137</v>
+      </c>
+      <c r="B30" s="29"/>
+      <c r="C30" s="29"/>
+      <c r="D30" s="29"/>
+      <c r="E30" s="29"/>
+      <c r="F30" s="29"/>
+      <c r="G30" s="29"/>
+      <c r="H30" s="29"/>
+      <c r="I30" s="30" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="33" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="32" t="s">
+        <v>139</v>
+      </c>
+      <c r="B33" s="32"/>
+      <c r="C33" s="32"/>
+      <c r="D33" s="32"/>
+      <c r="E33" s="32"/>
+    </row>
+    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="10">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A7:H7"/>
     <mergeCell ref="A9:D9"/>
+    <mergeCell ref="L9:O9"/>
     <mergeCell ref="A16:F16"/>
+    <mergeCell ref="L16:Q16"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="A33:E33"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
